--- a/diseases/d135/1995-1999.xlsx
+++ b/diseases/d135/1995-1999.xlsx
@@ -716,17 +716,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -751,172 +751,101 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1995-01</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="O2" t="n">
+        <v>105</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -948,12 +877,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -978,50 +907,53 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1997-02-01</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1997-02</t>
+          <t>1995-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="O3" t="n">
+        <v>105</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
+          <t>Meningitis, Other Bacterial</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>registered_diagnoses</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1031,7 +963,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1041,12 +973,12 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>not_comparable</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1056,7 +988,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1066,12 +998,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1080,70 +1012,74 @@
         </is>
       </c>
       <c r="AN3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1106,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1205,172 +1141,101 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1997-03-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1997-03</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="O4" t="n">
+        <v>46</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1267,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1432,50 +1297,53 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1997-04-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1997-04</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="O5" t="n">
+        <v>46</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
+          <t>Meningitis, Other Bacterial</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>registered_diagnoses</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1485,7 +1353,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1495,12 +1363,12 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>not_comparable</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1510,7 +1378,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1520,12 +1388,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1534,70 +1402,74 @@
         </is>
       </c>
       <c r="AN5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1624,17 +1496,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1659,172 +1531,101 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1997-05-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1997-05</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="O6" t="n">
+        <v>64</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1856,12 +1657,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1886,50 +1687,53 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1997-06-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1997-06</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="O7" t="n">
+        <v>64</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
+          <t>Meningitis, Other Bacterial</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>registered_diagnoses</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1939,7 +1743,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1949,12 +1753,12 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>not_comparable</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1964,7 +1768,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -1974,12 +1778,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1988,70 +1792,74 @@
         </is>
       </c>
       <c r="AN7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2113,12 +1921,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1997-07-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1997-07</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -2340,12 +2148,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1997-08-01</t>
+          <t>1997-02-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1997-08</t>
+          <t>1997-02</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2567,12 +2375,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1997-09-01</t>
+          <t>1997-03-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1997-09</t>
+          <t>1997-03</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2794,12 +2602,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1997-10-01</t>
+          <t>1997-04-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1997-10</t>
+          <t>1997-04</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -3021,12 +2829,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1997-11-01</t>
+          <t>1997-05-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1997-11</t>
+          <t>1997-05</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -3248,12 +3056,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1997-06-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1997-12</t>
+          <t>1997-06</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -3475,12 +3283,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1997-07-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1997-07</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3702,12 +3510,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1998-02-01</t>
+          <t>1997-08-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1998-02</t>
+          <t>1997-08</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3929,12 +3737,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1998-03-01</t>
+          <t>1997-09-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1998-03</t>
+          <t>1997-09</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -4156,12 +3964,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1998-04-01</t>
+          <t>1997-10-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1998-04</t>
+          <t>1997-10</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -4383,12 +4191,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1998-05-01</t>
+          <t>1997-11-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1998-05</t>
+          <t>1997-11</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -4610,12 +4418,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1998-06-01</t>
+          <t>1997-12-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1998-06</t>
+          <t>1997-12</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -4802,17 +4610,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -4837,172 +4645,101 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1998-07-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1998-07</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="O20" t="n">
+        <v>43</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
-      <c r="AT20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5034,12 +4771,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -5064,50 +4801,53 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1998-08-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1998-08</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="O21" t="n">
+        <v>43</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
+          <t>Meningitis, Other Bacterial</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>registered_diagnoses</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -5117,7 +4857,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5127,12 +4867,12 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>not_comparable</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -5142,7 +4882,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
@@ -5152,12 +4892,12 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -5166,70 +4906,74 @@
         </is>
       </c>
       <c r="AN21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5291,12 +5035,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1998-09-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1998-09</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -5518,12 +5262,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1998-10-01</t>
+          <t>1998-02-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1998-10</t>
+          <t>1998-02</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -5745,12 +5489,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1998-11-01</t>
+          <t>1998-03-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1998-11</t>
+          <t>1998-03</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -5972,16 +5716,16 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1998-12-01</t>
+          <t>1998-04-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1998-12</t>
+          <t>1998-04</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -6199,12 +5943,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1998-05-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1998-05</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -6426,12 +6170,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1998-06-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1998-06</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -6653,12 +6397,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1998-07-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1998-07</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -6880,12 +6624,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1998-08-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1998-08</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -7107,12 +6851,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1998-09-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1998-09</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -7334,12 +7078,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1998-10-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1998-10</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -7561,12 +7305,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1998-11-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1998-11</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -7788,16 +7532,16 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1998-12-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1998-12</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -7980,17 +7724,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -8015,172 +7759,101 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="O34" t="n">
+        <v>63</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
-      <c r="AT34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV34" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8212,12 +7885,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -8242,172 +7915,179 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N35" t="n">
+        <v>63</v>
+      </c>
+      <c r="O35" t="n">
+        <v>63</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Meningitis, Other Bacterial</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
         <v>1</v>
       </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Heilahimnubólga af völdum sýkla</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D72_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP35" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
-      <c r="AT35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV35" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8149,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -8696,12 +8376,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -8860,6 +8540,2276 @@
         </is>
       </c>
       <c r="BC37" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1999-03-01</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1999-03</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1999-04-01</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1999-04</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1999-05-01</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1999-05</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1999-06-01</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1999-06</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1999-07-01</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1999-07</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1999-08-01</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1999-08</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1999-09-01</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1999-09</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1999-10-01</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1999-10</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1999-11-01</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1999-11</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>bacterial-meningitis</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D135</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Bacterial meningitis</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>细菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>1999-12</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_G00_BACTERIAL_MENINGITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Heilahimnubólga af völdum sýkla</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 G00; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
         <is>
           <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
@@ -8910,7 +10860,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1995-01-01</t>
         </is>
       </c>
     </row>
@@ -8981,7 +10931,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -8991,7 +10941,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
@@ -9011,7 +10961,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -9021,7 +10971,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -9032,7 +10982,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
     </row>
@@ -9043,7 +10993,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16">
